--- a/outputs/sour_cream/novus/primary_chain_output.xlsx
+++ b/outputs/sour_cream/novus/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01408153516990773</v>
+        <v>0.01408153516990551</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>4.706435460154828e-13</v>
+        <v>4.706435460152205e-13</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>3.085032729165042e-21</v>
+        <v>3.085032729165153e-21</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2188095675386463</v>
+        <v>0.2188095675386487</v>
       </c>
       <c r="C3" t="n">
         <v>0.04947047925942609</v>
@@ -580,7 +580,7 @@
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>3.969186107838014e-13</v>
+        <v>3.969186107841103e-13</v>
       </c>
       <c r="G3" t="n">
         <v>0.1</v>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.3418935830778411</v>
+        <v>0.3418935830778413</v>
       </c>
       <c r="N5" t="n">
         <v>178</v>
@@ -926,10 +926,10 @@
         <v>178</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1503321327484457</v>
+        <v>0.1503321327485221</v>
       </c>
       <c r="K2" t="n">
-        <v>0.53201805897649</v>
+        <v>0.532018058976545</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -1000,22 +1000,22 @@
         <v>176</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8049124174362647</v>
+        <v>0.8049124174362638</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3181803694069162</v>
+        <v>0.3181803694069161</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.9103202976511395</v>
+        <v>-0.9103202976511392</v>
       </c>
       <c r="M3" t="n">
-        <v>1.29361685195193e-25</v>
+        <v>1.293616851986384e-25</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2798213093974368</v>
+        <v>0.2798213093974461</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3401073440796139</v>
+        <v>0.3401073440796145</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9991919902903724</v>
+        <v>0.9991919902903723</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4332665662567991</v>
+        <v>0.4332665662563698</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02815203711815504</v>
+        <v>0.02815203711815678</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.07252573667137049</v>
+        <v>0.07252573667137008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01278306675389943</v>
+        <v>0.01278306675389984</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03261969684847455</v>
+        <v>0.03261969684847454</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -56986,10 +56986,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5272629908128263</v>
+        <v>0.5272629908128266</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.2776494266234383</v>
+        <v>-0.2776494266234373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -57002,10 +57002,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5660151486488385</v>
+        <v>0.5660151486488386</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.2980557790340312</v>
+        <v>-0.2980557790340301</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -57018,10 +57018,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.5688633093639157</v>
+        <v>0.5688633093639158</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.2995555812262039</v>
+        <v>-0.2995555812262027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -57034,10 +57034,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5690726401447521</v>
+        <v>0.5690726401447522</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2996658119313484</v>
+        <v>-0.2996658119313472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -57050,10 +57050,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.5690880252933407</v>
+        <v>0.5690880252933408</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.299673913538627</v>
+        <v>-0.2996739135386258</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -57066,10 +57066,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5690891560529745</v>
+        <v>0.5690891560529747</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.2996745089810712</v>
+        <v>-0.29967450898107</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -57082,10 +57082,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5690892391602219</v>
+        <v>0.569089239160222</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.2996745527442027</v>
+        <v>-0.2996745527442015</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -57098,10 +57098,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.569089245268341</v>
+        <v>0.5690892452683411</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2996745559606541</v>
+        <v>-0.2996745559606528</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -57114,10 +57114,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5690892457172685</v>
+        <v>0.5690892457172686</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.2996745561970531</v>
+        <v>-0.2996745561970519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -57130,10 +57130,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5690892457502632</v>
+        <v>0.5690892457502633</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.2996745562144276</v>
+        <v>-0.2996745562144264</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -57146,10 +57146,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5690892457526882</v>
+        <v>0.5690892457526884</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.2996745562157046</v>
+        <v>-0.2996745562157034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -57162,10 +57162,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5690892457528665</v>
+        <v>0.5690892457528666</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.2996745562157985</v>
+        <v>-0.2996745562157972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -57178,10 +57178,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5690892457528796</v>
+        <v>0.5690892457528797</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.2996745562158054</v>
+        <v>-0.2996745562158041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -57194,10 +57194,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5690892457528804</v>
+        <v>0.5690892457528807</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.2996745562158059</v>
+        <v>-0.2996745562158046</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -57210,10 +57210,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.5690892457528806</v>
+        <v>0.5690892457528807</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.2996745562158059</v>
+        <v>-0.2996745562158047</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -57226,10 +57226,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5690892457528806</v>
+        <v>0.5690892457528807</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.2996745562158059</v>
+        <v>-0.2996745562158047</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -57242,10 +57242,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5690892457528806</v>
+        <v>0.5690892457528807</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.2996745562158059</v>
+        <v>-0.2996745562158047</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -57258,10 +57258,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.5690892457528806</v>
+        <v>0.5690892457528807</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2996745562158059</v>
+        <v>-0.2996745562158047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -57274,10 +57274,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.5690892457528806</v>
+        <v>0.5690892457528807</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.2996745562158059</v>
+        <v>-0.2996745562158047</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -57290,10 +57290,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5690892457528806</v>
+        <v>0.5690892457528807</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.2996745562158059</v>
+        <v>-0.2996745562158047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -57306,10 +57306,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.5690892457528806</v>
+        <v>0.5690892457528807</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.2996745562158059</v>
+        <v>-0.2996745562158047</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
